--- a/templates/PlantillaReporte.xlsx
+++ b/templates/PlantillaReporte.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
   <si>
     <t xml:space="preserve">SOLICITUD DE RECIBO</t>
   </si>
@@ -139,12 +139,6 @@
   </si>
   <si>
     <t>{lider}</t>
-  </si>
-  <si>
-    <t>COLABORADOR(ES)</t>
-  </si>
-  <si>
-    <t>{colaborador}</t>
   </si>
   <si>
     <t>{socio}</t>
@@ -240,7 +234,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="18">
+  <borders count="15">
     <border>
       <left style="none"/>
       <right style="none"/>
@@ -381,33 +375,6 @@
         <color auto="1"/>
       </top>
       <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right/>
-      <top style="none"/>
-      <bottom style="thin">
-        <color theme="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="none"/>
-      <bottom style="thin">
-        <color theme="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="thin">
-        <color theme="1"/>
-      </bottom>
       <diagonal style="none"/>
     </border>
     <border>
@@ -423,7 +390,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="51">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="1" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf fontId="1" fillId="2" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -509,13 +476,7 @@
     <xf fontId="6" fillId="2" borderId="14" numFmtId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment shrinkToFit="1"/>
     </xf>
-    <xf fontId="6" fillId="2" borderId="15" numFmtId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment shrinkToFit="1"/>
-    </xf>
-    <xf fontId="6" fillId="2" borderId="16" numFmtId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment shrinkToFit="1"/>
-    </xf>
-    <xf fontId="8" fillId="2" borderId="17" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="8" fillId="2" borderId="14" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf fontId="6" fillId="2" borderId="0" numFmtId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1491,10 +1452,10 @@
       <c r="C32" s="40" t="s">
         <v>32</v>
       </c>
-      <c r="D32" s="41"/>
-      <c r="E32" s="41"/>
-      <c r="F32" s="42"/>
-      <c r="G32" s="43"/>
+      <c r="D32" s="40"/>
+      <c r="E32" s="40"/>
+      <c r="F32" s="40"/>
+      <c r="G32" s="41"/>
       <c r="H32" s="5"/>
       <c r="I32" s="6"/>
     </row>
@@ -1515,12 +1476,12 @@
         <v>33</v>
       </c>
       <c r="C34" s="7"/>
-      <c r="D34" s="44" t="s">
+      <c r="D34" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="E34" s="45"/>
-      <c r="F34" s="45"/>
-      <c r="G34" s="45"/>
+      <c r="E34" s="43"/>
+      <c r="F34" s="43"/>
+      <c r="G34" s="43"/>
       <c r="H34" s="5"/>
       <c r="I34" s="6"/>
     </row>
@@ -1589,12 +1550,12 @@
         <v>37</v>
       </c>
       <c r="C40" s="5"/>
-      <c r="D40" s="46" t="s">
+      <c r="D40" s="44" t="s">
         <v>38</v>
       </c>
       <c r="E40" s="14"/>
-      <c r="F40" s="47"/>
-      <c r="G40" s="47"/>
+      <c r="F40" s="45"/>
+      <c r="G40" s="45"/>
       <c r="H40" s="5"/>
       <c r="I40" s="6"/>
     </row>
@@ -1604,84 +1565,69 @@
         <v>39</v>
       </c>
       <c r="C41" s="5"/>
-      <c r="D41" s="46" t="s">
+      <c r="D41" s="44" t="s">
         <v>40</v>
       </c>
       <c r="E41" s="14"/>
-      <c r="F41" s="47"/>
-      <c r="G41" s="47"/>
+      <c r="F41" s="45"/>
+      <c r="G41" s="45"/>
       <c r="H41" s="5"/>
       <c r="I41" s="6"/>
     </row>
     <row r="42" ht="14.25">
       <c r="A42" s="4"/>
-      <c r="B42" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="C42" s="5"/>
-      <c r="D42" s="46" t="s">
-        <v>42</v>
-      </c>
-      <c r="E42" s="14"/>
-      <c r="F42" s="47"/>
-      <c r="G42" s="47"/>
+      <c r="B42" s="20"/>
+      <c r="C42" s="7"/>
+      <c r="D42" s="5"/>
+      <c r="E42" s="5"/>
+      <c r="F42" s="5"/>
+      <c r="G42" s="5"/>
       <c r="H42" s="5"/>
       <c r="I42" s="6"/>
     </row>
-    <row r="43" ht="14.25">
+    <row r="43" ht="26" customHeight="1">
       <c r="A43" s="4"/>
-      <c r="B43" s="20"/>
-      <c r="C43" s="7"/>
+      <c r="B43" s="46" t="s">
+        <v>41</v>
+      </c>
+      <c r="C43" s="47"/>
       <c r="D43" s="5"/>
       <c r="E43" s="5"/>
       <c r="F43" s="5"/>
-      <c r="G43" s="5"/>
-      <c r="H43" s="5"/>
+      <c r="G43" s="46" t="s">
+        <v>42</v>
+      </c>
+      <c r="H43" s="48"/>
       <c r="I43" s="6"/>
     </row>
-    <row r="44" ht="26" customHeight="1">
+    <row r="44" ht="14.25">
       <c r="A44" s="4"/>
-      <c r="B44" s="48" t="s">
+      <c r="B44" s="49" t="s">
         <v>43</v>
       </c>
       <c r="C44" s="49"/>
-      <c r="D44" s="5"/>
-      <c r="E44" s="5"/>
-      <c r="F44" s="5"/>
-      <c r="G44" s="48" t="s">
+      <c r="D44" s="7"/>
+      <c r="E44" s="7"/>
+      <c r="F44" s="7"/>
+      <c r="G44" s="49" t="s">
         <v>44</v>
       </c>
       <c r="H44" s="50"/>
       <c r="I44" s="6"/>
     </row>
-    <row r="45" ht="14.25">
-      <c r="A45" s="4"/>
-      <c r="B45" s="51" t="s">
-        <v>45</v>
-      </c>
-      <c r="C45" s="51"/>
-      <c r="D45" s="7"/>
-      <c r="E45" s="7"/>
-      <c r="F45" s="7"/>
-      <c r="G45" s="51" t="s">
-        <v>46</v>
-      </c>
-      <c r="H45" s="52"/>
-      <c r="I45" s="6"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="16"/>
-      <c r="B46" s="17"/>
-      <c r="C46" s="17"/>
-      <c r="D46" s="17"/>
-      <c r="E46" s="17"/>
-      <c r="F46" s="17"/>
-      <c r="G46" s="17"/>
-      <c r="H46" s="17"/>
-      <c r="I46" s="19"/>
+    <row r="45">
+      <c r="A45" s="16"/>
+      <c r="B45" s="17"/>
+      <c r="C45" s="17"/>
+      <c r="D45" s="17"/>
+      <c r="E45" s="17"/>
+      <c r="F45" s="17"/>
+      <c r="G45" s="17"/>
+      <c r="H45" s="17"/>
+      <c r="I45" s="19"/>
     </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="16">
     <mergeCell ref="A6:I6"/>
     <mergeCell ref="A7:I7"/>
     <mergeCell ref="C13:G13"/>
@@ -1695,10 +1641,9 @@
     <mergeCell ref="D34:G34"/>
     <mergeCell ref="D40:E40"/>
     <mergeCell ref="D41:E41"/>
-    <mergeCell ref="D42:E42"/>
+    <mergeCell ref="B43:C43"/>
     <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="G45:H45"/>
+    <mergeCell ref="G44:H44"/>
   </mergeCells>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
